--- a/docs/WeaponHero_TC.xlsx
+++ b/docs/WeaponHero_TC.xlsx
@@ -9,9 +9,10 @@
   <sheets>
     <sheet name="요약" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="TC 목록" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="자동화" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="결함" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="범위 밖 · 이연" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="결과 보고서" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="자동화" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="결함" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="범위 밖 · 이연" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'TC 목록'!$A$1:$M$110</definedName>
@@ -25,7 +26,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,6 +63,11 @@
       <name val="Arial"/>
       <b val="1"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00595959"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="4">
@@ -108,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -125,6 +131,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -234,6 +242,140 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>영역별 Pass / Fail</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="stacked"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'결과 보고서'!B15</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'결과 보고서'!$A$16:$A$26</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'결과 보고서'!$B$16:$B$26</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'결과 보고서'!C15</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'결과 보고서'!$A$16:$A$26</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'결과 보고서'!$C$16:$C$26</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <overlap val="100"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7920000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5953,6 +6095,600 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="96" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>1회전 테스트 결과 보고서</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>대상 빌드 v1.0 (2026-09-03 제출본) · 수행 2026-09-23 ~ 09-24 · 세션 8회</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>테스트 정보</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>담당 QA</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>손주환 (1명)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>테스트 기간</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23 ~ 2026-09-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>테스트 빌드</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>v1.0 · Windows x64</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>플랫폼</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Windows · 단독 실행</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>테스트 환경</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Windows 11 Home 24H2 · Ryzen 5 9600X · RX 9070 XT · 32GB · 2560×1440</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>엔진</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Unity 6000.3.15f1 · URP 2D</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>테스트 방법</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>수동(빌드) + 수동(에디터) + 자동(EditMode 21개)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>영역별 테스트 요약</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>영역</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>성공률</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>이동 · 점프</t>
+        </is>
+      </c>
+      <c r="B16" s="3">
+        <f>COUNTIFS('TC 목록'!$B$2:$B$110,$A16,'TC 목록'!$H$2:$H$110,"Pass")</f>
+        <v/>
+      </c>
+      <c r="C16" s="3">
+        <f>COUNTIFS('TC 목록'!$B$2:$B$110,$A16,'TC 목록'!$H$2:$H$110,"Fail")</f>
+        <v/>
+      </c>
+      <c r="D16" s="3">
+        <f>COUNTIFS('TC 목록'!$B$2:$B$110,$A16,'TC 목록'!$H$2:$H$110,"N/A")</f>
+        <v/>
+      </c>
+      <c r="E16" s="3">
+        <f>COUNTIF('TC 목록'!$B$2:$B$110,$A16)</f>
+        <v/>
+      </c>
+      <c r="F16" s="6">
+        <f>IFERROR(B16/E16,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>전투 · 피격</t>
+        </is>
+      </c>
+      <c r="B17" s="3">
+        <f>COUNTIFS('TC 목록'!$B$2:$B$110,$A17,'TC 목록'!$H$2:$H$110,"Pass")</f>
+        <v/>
+      </c>
+      <c r="C17" s="3">
+        <f>COUNTIFS('TC 목록'!$B$2:$B$110,$A17,'TC 목록'!$H$2:$H$110,"Fail")</f>
+        <v/>
+      </c>
+      <c r="D17" s="3">
+        <f>COUNTIFS('TC 목록'!$B$2:$B$110,$A17,'TC 목록'!$H$2:$H$110,"N/A")</f>
+        <v/>
+      </c>
+      <c r="E17" s="3">
+        <f>COUNTIF('TC 목록'!$B$2:$B$110,$A17)</f>
+        <v/>
+      </c>
+      <c r="F17" s="6">
+        <f>IFERROR(B17/E17,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>무기 스왑</t>
+        </is>
+      </c>
+      <c r="B18" s="3">
+        <f>COUNTIFS('TC 목록'!$B$2:$B$110,$A18,'TC 목록'!$H$2:$H$110,"Pass")</f>
+        <v/>
+      </c>
+      <c r="C18" s="3">
+        <f>COUNTIFS('TC 목록'!$B$2:$B$110,$A18,'TC 목록'!$H$2:$H$110,"Fail")</f>
+        <v/>
+      </c>
+      <c r="D18" s="3">
+        <f>COUNTIFS('TC 목록'!$B$2:$B$110,$A18,'TC 목록'!$H$2:$H$110,"N/A")</f>
+        <v/>
+      </c>
+      <c r="E18" s="3">
+        <f>COUNTIF('TC 목록'!$B$2:$B$110,$A18)</f>
+        <v/>
+      </c>
+      <c r="F18" s="6">
+        <f>IFERROR(B18/E18,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>무기 · 투사체</t>
+        </is>
+      </c>
+      <c r="B19" s="3">
+        <f>COUNTIFS('TC 목록'!$B$2:$B$110,$A19,'TC 목록'!$H$2:$H$110,"Pass")</f>
+        <v/>
+      </c>
+      <c r="C19" s="3">
+        <f>COUNTIFS('TC 목록'!$B$2:$B$110,$A19,'TC 목록'!$H$2:$H$110,"Fail")</f>
+        <v/>
+      </c>
+      <c r="D19" s="3">
+        <f>COUNTIFS('TC 목록'!$B$2:$B$110,$A19,'TC 목록'!$H$2:$H$110,"N/A")</f>
+        <v/>
+      </c>
+      <c r="E19" s="3">
+        <f>COUNTIF('TC 목록'!$B$2:$B$110,$A19)</f>
+        <v/>
+      </c>
+      <c r="F19" s="6">
+        <f>IFERROR(B19/E19,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>적 · 보스</t>
+        </is>
+      </c>
+      <c r="B20" s="3">
+        <f>COUNTIFS('TC 목록'!$B$2:$B$110,$A20,'TC 목록'!$H$2:$H$110,"Pass")</f>
+        <v/>
+      </c>
+      <c r="C20" s="3">
+        <f>COUNTIFS('TC 목록'!$B$2:$B$110,$A20,'TC 목록'!$H$2:$H$110,"Fail")</f>
+        <v/>
+      </c>
+      <c r="D20" s="3">
+        <f>COUNTIFS('TC 목록'!$B$2:$B$110,$A20,'TC 목록'!$H$2:$H$110,"N/A")</f>
+        <v/>
+      </c>
+      <c r="E20" s="3">
+        <f>COUNTIF('TC 목록'!$B$2:$B$110,$A20)</f>
+        <v/>
+      </c>
+      <c r="F20" s="6">
+        <f>IFERROR(B20/E20,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>방 · 스테이지</t>
+        </is>
+      </c>
+      <c r="B21" s="3">
+        <f>COUNTIFS('TC 목록'!$B$2:$B$110,$A21,'TC 목록'!$H$2:$H$110,"Pass")</f>
+        <v/>
+      </c>
+      <c r="C21" s="3">
+        <f>COUNTIFS('TC 목록'!$B$2:$B$110,$A21,'TC 목록'!$H$2:$H$110,"Fail")</f>
+        <v/>
+      </c>
+      <c r="D21" s="3">
+        <f>COUNTIFS('TC 목록'!$B$2:$B$110,$A21,'TC 목록'!$H$2:$H$110,"N/A")</f>
+        <v/>
+      </c>
+      <c r="E21" s="3">
+        <f>COUNTIF('TC 목록'!$B$2:$B$110,$A21)</f>
+        <v/>
+      </c>
+      <c r="F21" s="6">
+        <f>IFERROR(B21/E21,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>런 루프 · 보상</t>
+        </is>
+      </c>
+      <c r="B22" s="3">
+        <f>COUNTIFS('TC 목록'!$B$2:$B$110,$A22,'TC 목록'!$H$2:$H$110,"Pass")</f>
+        <v/>
+      </c>
+      <c r="C22" s="3">
+        <f>COUNTIFS('TC 목록'!$B$2:$B$110,$A22,'TC 목록'!$H$2:$H$110,"Fail")</f>
+        <v/>
+      </c>
+      <c r="D22" s="3">
+        <f>COUNTIFS('TC 목록'!$B$2:$B$110,$A22,'TC 목록'!$H$2:$H$110,"N/A")</f>
+        <v/>
+      </c>
+      <c r="E22" s="3">
+        <f>COUNTIF('TC 목록'!$B$2:$B$110,$A22)</f>
+        <v/>
+      </c>
+      <c r="F22" s="6">
+        <f>IFERROR(B22/E22,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>UI · 설정 · 로컬라이즈</t>
+        </is>
+      </c>
+      <c r="B23" s="3">
+        <f>COUNTIFS('TC 목록'!$B$2:$B$110,$A23,'TC 목록'!$H$2:$H$110,"Pass")</f>
+        <v/>
+      </c>
+      <c r="C23" s="3">
+        <f>COUNTIFS('TC 목록'!$B$2:$B$110,$A23,'TC 목록'!$H$2:$H$110,"Fail")</f>
+        <v/>
+      </c>
+      <c r="D23" s="3">
+        <f>COUNTIFS('TC 목록'!$B$2:$B$110,$A23,'TC 목록'!$H$2:$H$110,"N/A")</f>
+        <v/>
+      </c>
+      <c r="E23" s="3">
+        <f>COUNTIF('TC 목록'!$B$2:$B$110,$A23)</f>
+        <v/>
+      </c>
+      <c r="F23" s="6">
+        <f>IFERROR(B23/E23,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>소리</t>
+        </is>
+      </c>
+      <c r="B24" s="3">
+        <f>COUNTIFS('TC 목록'!$B$2:$B$110,$A24,'TC 목록'!$H$2:$H$110,"Pass")</f>
+        <v/>
+      </c>
+      <c r="C24" s="3">
+        <f>COUNTIFS('TC 목록'!$B$2:$B$110,$A24,'TC 목록'!$H$2:$H$110,"Fail")</f>
+        <v/>
+      </c>
+      <c r="D24" s="3">
+        <f>COUNTIFS('TC 목록'!$B$2:$B$110,$A24,'TC 목록'!$H$2:$H$110,"N/A")</f>
+        <v/>
+      </c>
+      <c r="E24" s="3">
+        <f>COUNTIF('TC 목록'!$B$2:$B$110,$A24)</f>
+        <v/>
+      </c>
+      <c r="F24" s="6">
+        <f>IFERROR(B24/E24,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>경계 · 비정상 흐름</t>
+        </is>
+      </c>
+      <c r="B25" s="3">
+        <f>COUNTIFS('TC 목록'!$B$2:$B$110,$A25,'TC 목록'!$H$2:$H$110,"Pass")</f>
+        <v/>
+      </c>
+      <c r="C25" s="3">
+        <f>COUNTIFS('TC 목록'!$B$2:$B$110,$A25,'TC 목록'!$H$2:$H$110,"Fail")</f>
+        <v/>
+      </c>
+      <c r="D25" s="3">
+        <f>COUNTIFS('TC 목록'!$B$2:$B$110,$A25,'TC 목록'!$H$2:$H$110,"N/A")</f>
+        <v/>
+      </c>
+      <c r="E25" s="3">
+        <f>COUNTIF('TC 목록'!$B$2:$B$110,$A25)</f>
+        <v/>
+      </c>
+      <c r="F25" s="6">
+        <f>IFERROR(B25/E25,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>빌드 전 정적 확인</t>
+        </is>
+      </c>
+      <c r="B26" s="3">
+        <f>COUNTIFS('TC 목록'!$B$2:$B$110,$A26,'TC 목록'!$H$2:$H$110,"Pass")</f>
+        <v/>
+      </c>
+      <c r="C26" s="3">
+        <f>COUNTIFS('TC 목록'!$B$2:$B$110,$A26,'TC 목록'!$H$2:$H$110,"Fail")</f>
+        <v/>
+      </c>
+      <c r="D26" s="3">
+        <f>COUNTIFS('TC 목록'!$B$2:$B$110,$A26,'TC 목록'!$H$2:$H$110,"N/A")</f>
+        <v/>
+      </c>
+      <c r="E26" s="3">
+        <f>COUNTIF('TC 목록'!$B$2:$B$110,$A26)</f>
+        <v/>
+      </c>
+      <c r="F26" s="6">
+        <f>IFERROR(B26/E26,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="B27" s="7">
+        <f>SUM(B16:B26)</f>
+        <v/>
+      </c>
+      <c r="C27" s="7">
+        <f>SUM(C16:C26)</f>
+        <v/>
+      </c>
+      <c r="D27" s="7">
+        <f>SUM(D16:D26)</f>
+        <v/>
+      </c>
+      <c r="E27" s="7">
+        <f>SUM(E16:E26)</f>
+        <v/>
+      </c>
+      <c r="F27" s="13">
+        <f>IFERROR(B27/E27,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>결과 리포트</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>미확인 0건</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>시작 시 △ 6건이 전부 해소됐다. 확인 못 한 항목을 통과로 적지 않는 것이 이 표의 규칙이므로, 0 은 모든 항목에 대해 봤거나 못 본 이유가 적혀 있다는 뜻이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>Major 셋의 공통점</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>#153 #150 #149 는 전부 "동작은 하는데 읽을 수 없다"에 해당한다. #150 은 보스 패턴이 안 끊기므로 예고가 유일한 회피 신호라는 점에서 특히 무겁다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>#149 가 Critical 이 아닌 이유</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>TC-EDGE-14(재선택 불가)가 통과해, 패널이 남아도 보상이 두 번 적용되지 않는 것을 확인했다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>Trivial 을 남긴 이유</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>#154 는 매 실행마다 뜨는 오탐 경고다. 두면 진짜 배선 누락이 같은 줄에 섞인다 — W3 에서 HurtBox.health 를 놓친 것이 그 종류였다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>과거 수정분 4건</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>TC-UI-01 · UI-07 · ROOM-04 · RUN-08 의 수정이 유지되는 것을 확인했다. ROOM-04 는 자동 테스트로 승격돼 사람이 다시 안 본다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>이연 1건</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>TC-CMB-08 은 재현됐고 고치지 않는다. 범위가 1차에 없다는 근거가 기록에 있고, 이번 수행의 목적은 그 판단이 유효한지 보는 것이었다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>실패의 출처</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>신규 7건 중 셋(UI-12 · UI-13 · BLD-10)이 수행 목록이 아니라 캡처와 로그에서 나왔다. 2회전에는 캡처 검토와 로그 확인을 세션 단계로 넣는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>TC 자체의 결함</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>존재하지 않는 조작(EDGE-22) · 한 항목이 두 대상(EDGE-23) · 규칙이 다른 둘을 묶음(ENM-03). 수행은 제품만이 아니라 TC 도 검사한다.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -6756,7 +7492,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7148,7 +7884,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
